--- a/public/modelos/biblioteca-v2/PCM-MAN-013_Auditorias-da-Manutencao_R00.xlsx
+++ b/public/modelos/biblioteca-v2/PCM-MAN-013_Auditorias-da-Manutencao_R00.xlsx
@@ -1017,12 +1017,12 @@
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
-        <t>Setor.</t>
+        <t>Família de equipamento.</t>
       </text>
     </comment>
     <comment ref="J3" authorId="0" shapeId="0">
       <text>
-        <t>Família de equipamento.</t>
+        <t>Setor.</t>
       </text>
     </comment>
   </commentList>
@@ -1311,20 +1311,20 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tb_pcm_setores" displayName="tb_pcm_setores" ref="H4:H29" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tb_pcm_familias" displayName="tb_pcm_familias" ref="H4:H29" headerRowCount="1">
   <autoFilter ref="H4:H29"/>
   <tableColumns count="1">
-    <tableColumn id="8" name="nome_setor"/>
+    <tableColumn id="8" name="nome_familia"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tb_pcm_familias" displayName="tb_pcm_familias" ref="J4:J29" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tb_pcm_setores" displayName="tb_pcm_setores" ref="J4:J29" headerRowCount="1">
   <autoFilter ref="J4:J29"/>
   <tableColumns count="1">
-    <tableColumn id="10" name="nome_familia"/>
+    <tableColumn id="10" name="nome_setor"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
 </table>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="D19" s="33" t="inlineStr">
         <is>
-          <t>Cadastre uma vez TAG, equipamento, família e setor, as pessoas, os setores, as famílias de equipamento. Eles aparecem nas setas ▼ das outras abas.</t>
+          <t>Cadastre uma vez TAG, equipamento, família e setor, as pessoas, as famílias de equipamento, os setores. Eles aparecem nas setas ▼ das outras abas.</t>
         </is>
       </c>
       <c r="E19" s="34" t="n"/>
@@ -3567,9 +3567,9 @@
     <col width="3" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="3" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
     <col width="3" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="H3" s="91" t="inlineStr">
         <is>
+          <t>Família de equipamento</t>
+        </is>
+      </c>
+      <c r="J3" s="91" t="inlineStr">
+        <is>
           <t>Setor</t>
-        </is>
-      </c>
-      <c r="J3" s="91" t="inlineStr">
-        <is>
-          <t>Família de equipamento</t>
         </is>
       </c>
     </row>
@@ -3675,12 +3675,12 @@
       </c>
       <c r="H4" s="77" t="inlineStr">
         <is>
+          <t>nome_familia</t>
+        </is>
+      </c>
+      <c r="J4" s="77" t="inlineStr">
+        <is>
           <t>nome_setor</t>
-        </is>
-      </c>
-      <c r="J4" s="77" t="inlineStr">
-        <is>
-          <t>nome_familia</t>
         </is>
       </c>
     </row>
